--- a/bulk-questions-template.xlsx
+++ b/bulk-questions-template.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BulkQuestions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +26,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0024446F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +56,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,110 +437,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>grade</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>skill</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>choice1</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>choice2</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>choice3</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>choice4</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>image</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Choice 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Choice 2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Choice 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Choice 4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Correct Answer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Skill (optional)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Type (optional)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Image (optional)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Difficulty 1-3 (optional)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Note (optional)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>kg1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KG1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>What color is the sun?</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Vocabulary</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>What animal is this?</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Bird</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Fish</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>cat.svg</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Example row</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>How to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. Fill one row per question in BulkQuestions sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2. KG must be KG1 or KG2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3. Correct Answer must match one of the four choices exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4. Optional columns can be left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5. Upload the filled file from Admin &gt; Bulk Question Import.</t>
         </is>
       </c>
     </row>
